--- a/Example/Extract Pandat Results/Ts-S.xlsx
+++ b/Example/Extract Pandat Results/Ts-S.xlsx
@@ -586,6 +586,9 @@
       <c r="C12">
         <v>90</v>
       </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
       <c r="E12">
         <v>10</v>
       </c>
@@ -603,6 +606,9 @@
       <c r="D13">
         <v>10</v>
       </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
@@ -770,6 +776,9 @@
       <c r="D23">
         <v>1</v>
       </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
@@ -933,6 +942,9 @@
       </c>
       <c r="C33">
         <v>99</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -985,6 +997,9 @@
       <c r="D36">
         <v>2</v>
       </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
@@ -1114,6 +1129,9 @@
       </c>
       <c r="C44">
         <v>98</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -1183,6 +1201,9 @@
       <c r="D48">
         <v>3</v>
       </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
@@ -1295,6 +1316,9 @@
       </c>
       <c r="C55">
         <v>97</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -1381,6 +1405,9 @@
       <c r="D60">
         <v>4</v>
       </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
@@ -1476,6 +1503,9 @@
       </c>
       <c r="C66">
         <v>96</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -1579,6 +1609,9 @@
       <c r="D72">
         <v>5</v>
       </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
@@ -1657,6 +1690,9 @@
       </c>
       <c r="C77">
         <v>95</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
       </c>
       <c r="E77">
         <v>5</v>
@@ -1777,6 +1813,9 @@
       <c r="D84">
         <v>6</v>
       </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
@@ -1838,6 +1877,9 @@
       </c>
       <c r="C88">
         <v>94</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
       </c>
       <c r="E88">
         <v>6</v>
@@ -1975,6 +2017,9 @@
       <c r="D96">
         <v>7</v>
       </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
@@ -2019,6 +2064,9 @@
       </c>
       <c r="C99">
         <v>93</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
       </c>
       <c r="E99">
         <v>7</v>
@@ -2173,6 +2221,9 @@
       <c r="D108">
         <v>8</v>
       </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
@@ -2200,6 +2251,9 @@
       </c>
       <c r="C110">
         <v>92</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
       </c>
       <c r="E110">
         <v>8</v>
@@ -2371,6 +2425,9 @@
       <c r="D120">
         <v>9</v>
       </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
@@ -2381,6 +2438,9 @@
       </c>
       <c r="C121">
         <v>91</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
       </c>
       <c r="E121">
         <v>9</v>
@@ -2395,6 +2455,12 @@
       </c>
       <c r="C122">
         <v>100</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
